--- a/신고신저가_20260815.xlsx
+++ b/신고신저가_20260815.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,18 +77,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,74 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 사상최고 이튿날 소비지표 둔화로 미국 되돌림 — 조정은 소프트웨어·AI에 국한, 폭은 금융·에너지가 떠받친 로테이션 국면(추정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/14): S&amp;P500 7,785.76 -0.17%·나스닥 26,729.16 -0.28%·다우 53,732.41 -0.20%. 전일 사상최고(7,800 첫 돌파) 되돌림, 7월 소매판매 -0.6%로 소비 둔화 확인. 주간 기준은 3주 연속 상승 유지. 섹터 갈림 — 에너지 XLE +1.4%(주간 +7.7%, YTD 40.4% 전체 1위, 호르무즈 봉쇄 재개發 유가 강세), 유틸 +0.6%·커뮤니케이션·산업재·소재 +0.4% / 헬스케어 -0.6%·테크 -0.4%. 신고가 81(NEW 24)·신저가 8(NEW 2)로 폭은 여전히 넓음. 금융 순강도 +25로 압도적(12MF PER 중앙값 15.4) — 지역은행(시티즌스·컬렌프로스트·사우스스테이트)·캐나다은행(CIBC·BNS·BMO)·슈왑·캐피털원 전방위. 테크서비스는 순강도 +17이나 종목 다수가 52주 고가권에서 당일 급락(팔란티어 -2.8%, 크라우드스트라이크 -3.8%, 가이드와이어 -3.9%, 비바 -3.5%) — 고가권 이탈 조짐. 개별 신규 최고 — 누홀딩스 +9.3%(2분기 순이익 첫 10억달러 돌파), 폭스 +5.5%(FY4Q 매출 28%↑·월드컵 광고), 크라토스 +2.9%(대드론·시커 수주), 셰브런·코노코필립스 동반 신고가. 신규 신저 — 케이던스(EDA)가 장중 52주 저가 터치, 엔브리지 유가 랠리에서 소외</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/14): 닛케이225 68,713(+405, +0.6%) 4거래일 연속 상승, 토픽스 연중 최고. 신고가 19(NEW 1)·신저가 2. 업종 ETF 정보통신·서비스 +1.8%·운수물류 +1.6%·자동차 +1.4%·전기정밀 +1.3% / 의약품 -0.7%·부동산 -0.5%. 넥슨 +19.9%가 유일한 신규 최고 — 2분기 영업익 313억엔으로 컨센 240억엔 상회에 특별배당 415엔. 아식스 +10.8%(경상익 15% 상향·사상 첫 매출 1조엔 전망), 닌텐도 +6.9%, NEC +5.1%. 해운 3사 동반 신고가(가와사키기선 +4.4%·상선미쓰이 +3.1%·일본우선 +3.0%), 어드반테스트 +2.6% 사상 최고. 은행 5종은 고가권 유지하나 당일은 미즈호 -1.8% 등 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/14): 항셍 25,116.85 -1.10%·항셍테크 4,707.62 -1.77%. 항셍테크 YTD -14.7%, 52주 위치 19%로 중화권 최약. 신고가 4·신저가 2 모두 전일 승계. 전자기술 순강도 +2지만 레노버 -3.7%·차오저우삼환 -1.1%로 고가권에서 밀림. CLP홀딩스(전력)·SITC(해운) 방어 업종만 신고가 유지, 니오(전기차)·중국철도건설 신저가</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/14): 상해종합 3,927.18 +0.01%·CSI300 4,665.88 +0.04% 보합. 신고가 0·신저가 1(선전 JLC테크놀로지 -3.6%)로 방향성 부재. ETF는 성장 대 방어 갈림 — 5G통신 +2.8%·유색금속 +1.1%·반도체 +0.8%·테크 +0.8% / 백주 -1.8%·소비 -1.6%·의약 -1.5%·증권 -1.3%. 반도체 ETF는 YTD 47.1%로 여전히 A주 1위이나 1개월 -7.1%로 단기 조정 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①미 소매판매 둔화가 일회성인지 — 다음 주 소비 관련 지표와 유통 실적으로 확인 ②소프트웨어·AI 고가권 이탈이 며칠 더 이어지면 신고가 폭(현 81)이 먼저 줄어듦, 금융 순강도 +25 유지 여부가 로테이션 지속의 관건 ③호르무즈 봉쇄 장기화 시 에너지 주간 +7.7% 추가 연장 vs 인플레 재점화로 금리 되돌림 — 양방향</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 토요일 실행으로 전 시장 8/14(금) 마감 확정분. 미장은 KST 8/15 05:00 마감분(3시간 전). 닛케이 종가는 스크립트 index CSV가 8/13 기준이라 8/14 수치는 별도 확인분 사용. 중국A는 선행 PER 커버리지가 얇아(전자기술 71종목 중 38) 밸류 수치 미인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +781,19 @@
       <c r="C2" t="n">
         <v>7785.76</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.17</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>0.36</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>3.34</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>3.79</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>13.74</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +819,19 @@
       <c r="C3" t="n">
         <v>26729.16</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-0.28</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>0.14</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>3.27</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>15</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +857,19 @@
       <c r="C4" t="n">
         <v>6813.34</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>3.56</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-13.14</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>61.68</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +895,19 @@
       <c r="C5" t="n">
         <v>68308.59</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>1.16</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>3.03</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>1.59</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>9.029999999999999</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>35.7</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +933,19 @@
       <c r="C6" t="n">
         <v>3927.18</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>-0.33</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>1.15</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>-1.05</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +971,19 @@
       <c r="C7" t="n">
         <v>4665.88</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>-0.61</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-3.47</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>0.78</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1009,19 @@
       <c r="C8" t="n">
         <v>25116.85</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>-2.15</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.43</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>-4.82</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>-2</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1047,19 @@
       <c r="C9" t="n">
         <v>4707.62</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>-1.77</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>-2.62</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-7.26</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-14.65</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1178,7 @@
       <c r="F2" t="n">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1219,7 @@
       <c r="F3" t="n">
         <v>17</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1260,7 @@
       <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1301,7 @@
       <c r="F5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1342,7 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1383,7 @@
       <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1424,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1465,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1506,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1547,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1588,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1629,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1670,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1711,7 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1996,7 @@
       <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2037,7 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2076,7 @@
       <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2043,7 +2115,7 @@
       <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2084,7 +2156,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2123,7 +2195,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2162,7 +2234,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2203,7 +2275,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2242,7 +2314,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2675,7 +2747,7 @@
       <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2716,7 +2788,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2757,7 +2829,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2796,7 +2868,7 @@
       <c r="F44" t="n">
         <v>-1</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2837,7 +2909,7 @@
       <c r="F45" t="n">
         <v>-1</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3393,7 +3465,7 @@
       <c r="F59" t="n">
         <v>-1</v>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4097,30 +4169,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4141,90 +4214,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4246,58 +4324,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.4%·주간 +1.1%. 소프트웨어 고가권 이탈(크라우드스트라이크·비바 -3%대)이 지수 눌러 — YTD 32.3% 2위는 유지</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4317,58 +4400,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.6%로 당일 최약. 다만 3M +14.6%·신고가 8종목(머크·메드트로닉)으로 중기 추세는 살아있음</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4388,58 +4476,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.2%지만 신고가 25종목·순강도 +25로 전 섹터 1위. 지역은행·캐나다은행 전방위, 12MF PER 15.4로 밸류 부담 낮음</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4459,58 +4552,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.2%·YTD -0.6%로 11개 중 10위. 7월 소매판매 -0.6% 소비 둔화가 직격</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4530,58 +4628,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.4%. 폭스 +5.5%(월드컵 광고)·디즈니 +2.0% 미디어 강세, 다만 YTD -3.5%로 꼴찌</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4601,58 +4704,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.4%·YTD 20.9% 3위. 방산(노스럽·크라토스) 신규 신고가로 견인</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4672,58 +4780,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.1%. 소비 둔화 국면의 방어 수요, 다만 신고가 1종목뿐으로 폭은 없음</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4743,58 +4856,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.4%·주간 +7.7%·YTD 40.4%로 전 섹터 1위. 호르무즈 봉쇄 재개發 유가 강세, 셰브런·코노코 신규 신고가</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>40.4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4814,58 +4932,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.6%. 금리 되돌림 기대 방어 매수 추정, 1M -2.6%로 중기는 부진</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4885,58 +5008,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.4%. 은 가격 강세로 헤클라마이닝 신규 신고가, 에너지와 함께 당일 상위</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4956,58 +5084,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.3%. CBRE·JLL 부동산서비스 신규 신고가, 다만 1M -0.4%로 모멘텀은 약함</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5027,58 +5160,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5098,58 +5232,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5169,58 +5304,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>9.1</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5240,58 +5376,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5311,58 +5448,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>14</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5382,58 +5520,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5453,58 +5592,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>53.1</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5524,58 +5664,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5595,58 +5736,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5666,58 +5808,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5737,58 +5880,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5808,58 +5952,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>13</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5879,58 +6024,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-8.5</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5950,58 +6096,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6021,58 +6168,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>23.5</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>50.5</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6092,58 +6240,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>28.4</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6163,58 +6312,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-6.3</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6234,58 +6384,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6305,58 +6456,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-5.7</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6376,56 +6528,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-6.9</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-14.4</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6443,58 +6596,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.8%·YTD 47.1%로 A주 1위 유지. 1M -7.1% 단기 조정 중이나 당일은 반등</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-7.1</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>47.1</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6514,58 +6672,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.8%·YTD 33.5% 3위. 반도체와 동조 반등, 1M -5.1%로 조정 국면은 지속</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>33.5</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6585,58 +6748,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>1D +2.8%로 A주 ETF 중 최강. 주간 +3.0%로 통신 인프라 단기 순환매 추정</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6656,56 +6824,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.6%. 1M +4.3% 회복세지만 3M -17.9%·YTD -10.7%로 낙폭 과대 구간</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-17.9</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6723,58 +6896,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.3%. 3M -16.2%로 부진 지속, YTD -16.1%로 A주 하위권</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-16.2</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-16.1</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6794,56 +6972,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.2%. 1M +4.7% 반등 시도, 다만 3M -21.4%로 A주 최대 낙폭 업종</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-21.4</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-10.1</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6861,58 +7044,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.8%로 당일 최약. YTD -17.7%로 A주 꼴찌권, 소비 부진 직격</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-17.7</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>12</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6932,58 +7120,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.7%. 3M +3.4%로 방어력은 있으나 당일은 차익 실현</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7003,58 +7196,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.1%. 1M +9.6%로 A주 1위, 글로벌 금속 강세와 동조</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7074,58 +7272,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.2%·YTD -18.3%로 A주 최하위. 부동산 업황 반등 신호 부재</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7145,58 +7348,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.3%. 지수 보합에 거래대금 모멘텀 실종, 1M -2.3%</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-10.2</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7216,58 +7424,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.5%. 3M +13.2%로 중기 상위였던 만큼 차익 실현 추정</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7287,58 +7500,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.6%·YTD -15.1%. 백주와 함께 소비 섹터 동반 약세</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15.1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7350,7 +7568,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1.9"/>
@@ -7362,7 +7580,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-4.8"/>
@@ -7374,7 +7592,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-8.300000000000001"/>
@@ -7386,7 +7604,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-21.4"/>
@@ -7398,7 +7616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-18.3"/>
@@ -7410,7 +7628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7422,7 +7640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7434,7 +7652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7446,7 +7664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7458,7 +7676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7470,7 +7688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7584,7 +7802,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7633,15 +7851,15 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7685,10 +7903,10 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7741,15 +7959,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7795,10 +8013,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7847,10 +8065,10 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7903,15 +8121,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7955,15 +8173,15 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8007,10 +8225,10 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8059,10 +8277,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8115,10 +8333,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8167,10 +8385,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8223,10 +8441,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8279,15 +8497,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8331,10 +8549,14 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>엔브리지(캐나다 에너지 파이프라인): 개별 촉매 미확인 — 유가 강세에도 소외, 레버리지 부담 추정</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8387,10 +8609,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8443,10 +8665,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8499,15 +8721,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8551,15 +8773,15 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8603,15 +8825,19 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>케이던스디자인시스템즈(반도체 설계 EDA 소프트웨어): 소프트웨어 전반 조정 속 장중 52주 저가 터치 후 반등, 개별 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8655,15 +8881,19 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>카바나(중고차 온라인 플랫폼): 개별 촉매 미확인 — 실적 개선 기대 수급 추정</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8707,10 +8937,10 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8759,10 +8989,10 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8815,15 +9045,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8867,10 +9097,14 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>누홀딩스(브라질 디지털은행): 2분기 순이익 첫 10억달러 돌파(+49%), 컨센 상회</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8919,10 +9153,10 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8967,10 +9201,10 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9019,10 +9253,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9071,10 +9305,10 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9123,10 +9357,10 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9179,10 +9413,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9233,15 +9467,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9285,10 +9519,10 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9337,10 +9571,10 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9389,10 +9623,10 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9437,19 +9671,19 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr">
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>(전일) 아틀라시안(협업SW Jira·Confluence): 2분기 매출 28%↑·클라우드 31% 가속, Rovo AI 견인</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9497,10 +9731,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9549,10 +9783,10 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9603,14 +9837,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>(전일) 몽고DB(NoSQL 데이터베이스 SaaS): RBC·오펜하이머 목표가 대폭 상향, Atlas 성장 기대</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9663,10 +9897,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="7" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9715,10 +9949,10 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9767,10 +10001,10 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9819,15 +10053,15 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9875,15 +10109,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9931,15 +10165,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9983,10 +10217,14 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>폭스코퍼레이션(미디어·방송): FY26 4분기 매출 28%↑, 튜비 최대 실적·월드컵 광고 효과</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10035,10 +10273,10 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10087,10 +10325,10 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10139,14 +10377,14 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr">
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>(전일) 태피스트리(코치·케이트스페이드 핸드백): 4Q 서프라이즈에도 FY27 매출 가이던스 부진에 급락</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10195,10 +10433,10 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10247,15 +10485,15 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10303,10 +10541,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N52" s="7" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10359,10 +10597,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10415,10 +10653,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10467,10 +10705,10 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10519,14 +10757,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N56" s="7" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>(전일) 루브릭(데이터 백업·랜섬웨어 복구 SW): 보안·SW 랠리, BTIG 목표가 109달러 상향 여진</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10575,14 +10813,14 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>(전일) TPG(대체투자 운용사): 개별 뉴스 없음, 워크데이 인수설발 PE 딜 훈풍 추정</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10629,15 +10867,15 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10685,10 +10923,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10737,10 +10975,10 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10793,10 +11031,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10843,10 +11081,10 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10895,15 +11133,15 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10947,10 +11185,10 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11003,19 +11241,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="7" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>(전일) 롤린스(해충방제 서비스): 2분기 EPS 0.32달러로 컨센 하회·경영진 교체 우려로 52주 신저가</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11063,10 +11301,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11119,10 +11357,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11175,10 +11413,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="7" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11225,10 +11463,10 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="7" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11277,10 +11515,10 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="7" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11333,10 +11571,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N71" s="7" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11385,14 +11623,14 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="7" t="inlineStr">
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>(전일) 뉴로크린(신경정신질환 신약 개발): 프래더윌리 치료제 Vykat 사망사례 안전성 우려 보도</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11441,15 +11679,15 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11495,10 +11733,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="7" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11551,19 +11789,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="7" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>(전일) 무그(항공우주·방산 정밀제어시스템): 3분기 실적 호조·FY26 매출 가이던스 44억달러로 상향</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11607,10 +11845,10 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11659,15 +11897,15 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11711,15 +11949,19 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="7" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>헤클라마이닝(미국 은 광산): 개별 촉매 미확인 — 은·소재 섹터 강세 동조 추정</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11763,10 +12005,14 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>크라토스디펜스(무인기·방산 시스템): 재블린 시커·대드론 1.56억달러 등 수주 모멘텀</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11815,14 +12061,14 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr">
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>(전일) 도큐사인(전자서명·계약관리 SaaS): 개별 뉴스 없이 소프트웨어 업종 전반 랠리에 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11871,10 +12117,10 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11927,15 +12173,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11981,10 +12227,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N83" s="7" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12037,10 +12283,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N84" s="7" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12091,14 +12337,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N85" s="7" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>(전일) 글라우코스(녹내장·각막질환 의료기기): 2분기 매출 급증·2026년 가이던스 상향, 목표주가 잇단 상향</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12151,15 +12397,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N86" s="7" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12207,10 +12453,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12263,10 +12509,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N88" s="7" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr">
+        <is>
+          <t>달링인그리디언츠(동물부산물·재생연료 원료): 2분기 사상최대 실적·자사주 10억달러 여진</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12311,19 +12561,19 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="7" t="inlineStr">
+      <c r="N89" s="10" t="inlineStr">
         <is>
           <t>(전일) 허트8(비트코인 채굴·데이터센터): 2분기 순손실 전환, 75억달러 확장 파이낸싱 부담</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12371,7 +12621,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N90" s="7" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N90"/>
@@ -12477,7 +12727,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12524,10 +12774,10 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12580,14 +12830,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 어드반테스트(반도체 테스터 장비): AI 반도체 테스터 수요 급증·실적 상향으로 급등</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12640,14 +12890,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 미즈호FG(3대 메가뱅크): 당일 -1.5% 하락에도 장중 고가가 52주 신고가 터치, 은행 랠리 연장</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12694,14 +12944,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰비시중공업(중공업·방위산업): 방위비 증액 기대와 1분기 실적 호조 지속으로 상승</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12748,14 +12998,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) NTT(통신 1위): 개별 뉴스 없음, 금리·방어주 수급에 신고가 진입 추정</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12806,14 +13056,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 파나소닉(가전·전장·전지): 개별 뉴스 없음, 엔약세·전기정밀 섹터 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12862,14 +13112,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 닌텐도(게임기·소프트웨어): 인도네시아 스위치·스위치2 발매 추진 보도(지지통신)로 4개월래 최고가</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12918,14 +13168,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) NEC(IT서비스·통신장비): 당일 촉매 미확인, 1Q 순이익 +157%·가이던스 상향 모멘텀 연장 추정</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12972,14 +13222,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 다이킨(공조·에어컨): 8/4 1Q 순이익 -1.7% 발표 후 약세 지속, 당일 신규 악재는 없음</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13032,14 +13282,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 리소나홀딩스(대형 은행지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13092,14 +13342,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 스미토모미쓰이트러스트그룹(신탁은행 지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13146,14 +13396,14 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰비시지쇼(오피스 부동산 디벨로퍼): 특별한 뉴스 없음, 부동산 섹터 약세 수급 추정</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13200,14 +13450,14 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13258,14 +13508,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) LY Corporation(포털·메신저·페이페이 핀테크): 신규 촉매 없음, 8월초 페이페이발 호실적 모멘텀 연장</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13316,14 +13566,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 아식스(러닝화·스포츠용품): 2Q 경상이익 +48%, 연간 전망 1650→1890억엔 상향·증배, 상장래 최고가</t>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>아식스(스포츠용품 제조): 경상익 15% 상향 1890억엔, 사상 첫 매출 1조엔 전망</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13376,14 +13626,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>(전일) 니혼유센(벌크·컨테이너 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13432,15 +13682,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13482,10 +13732,14 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>넥슨(온라인게임 퍼블리셔): 2분기 영업익 313억엔으로 컨센 240억엔 상회, 특별배당 415엔</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13538,14 +13792,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>(전일) 지바은행(지방은행): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13598,10 +13852,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13654,7 +13908,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>(전일) 가와사키기선(컨테이너선 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
@@ -13764,7 +14018,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13817,14 +14071,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 레노버(PC·서버 세계 1위): FY26/27 1분기 매출 43%·조정순이익 176% 급증, AI서버 매출 사상 최고</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13873,14 +14127,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 차오저우싼환(적층세라믹콘덴서 MLCC·세라믹부품): AI 인프라용 고급 MLCC 공급부족·가격인상 수혜</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13931,14 +14185,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) CLP홀딩스(홍콩 최대 전력회사, 발전·송배전): 특별한 뉴스 없음(유틸리티 방어주 수급 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13991,14 +14245,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) SITC인터내셔널(아시아 역내 컨테이너 해운): 개별 뉴스 없음, 중간실적 앞둔 해운 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14049,14 +14303,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국철도건설(대형 인프라·철도 시공): 특별한 뉴스 없음(국유 건설섹터 수급 부진 추정)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14101,7 +14355,7 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 니오(중국 프리미엄 전기차): 특별한 뉴스 없음(전기차 섹터 수급 약세 추정)</t>
         </is>
@@ -14211,7 +14465,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14260,7 +14514,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 선전 자리촹(PCB·전자제조서비스, 8/4 상장): 개별 악재 없음, 상장 초기 급등 후 조정 지속 추정</t>
         </is>
